--- a/poker/resources/sample/dropDetailed.xlsx
+++ b/poker/resources/sample/dropDetailed.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="67">
   <si>
     <t>掉落ID</t>
   </si>
@@ -156,6 +156,78 @@
   </si>
   <si>
     <t>1000_1022502_1</t>
+  </si>
+  <si>
+    <t>赌场材料-40级</t>
+  </si>
+  <si>
+    <t>1434_1023001|717_1023101|359_1023101|120_1023201|60_1023401|60_1023301</t>
+  </si>
+  <si>
+    <t>赌场材料-50级</t>
+  </si>
+  <si>
+    <t>1447_1023001|724_1023101|362_1023101|121_1023201|60_1023401|60_1023301</t>
+  </si>
+  <si>
+    <t>赌场材料-60级</t>
+  </si>
+  <si>
+    <t>968_1023001|812_1023002|484_1023101|406_1023102|242_1023101|203_1023102|81_1023201|68_1023202|40_1023401|34_1023402|40_1023301|34_1023301</t>
+  </si>
+  <si>
+    <t>赌场材料-70级</t>
+  </si>
+  <si>
+    <t>265_1023001|889_1023002|133_1023101|445_1023102|66_1023101|222_1023102|22_1023201|74_1023202|11_1023401|37_1023402|11_1023301|37_1023301</t>
+  </si>
+  <si>
+    <t>赌场材料-80级</t>
+  </si>
+  <si>
+    <t>365_1023001|613_1023002|613_1023003|183_1023101|306_1023102|306_1023103|91_1023101|153_1023102|153_1023103|30_1023201|51_1023202|51_1023203|15_1023401|26_1023402|26_1023403|15_1023301|26_1023301|26_1023301</t>
+  </si>
+  <si>
+    <t>赌场材料-90级</t>
+  </si>
+  <si>
+    <t>223_1023002|893_1023003|112_1023102|447_1023103|56_1023102|223_1023103|19_1023202|74_1023203|9_1023402|37_1023403|9_1023301|37_1023301</t>
+  </si>
+  <si>
+    <t>赌场材料-100级</t>
+  </si>
+  <si>
+    <t>246_1023002|492_1023003|397_1023004|123_1023102|246_1023103|199_1023104|61_1023102|123_1023103|99_1023104|20_1023202|41_1023203|33_1023204|10_1023402|20_1023403|17_1023404|10_1023301|20_1023301|17_1023301</t>
+  </si>
+  <si>
+    <t>赌场材料-110级</t>
+  </si>
+  <si>
+    <t>264_1023003|853_1023004|132_1023103|427_1023104|66_1023103|213_1023104|22_1023203|71_1023204|11_1023403|36_1023404|11_1023301|36_1023301</t>
+  </si>
+  <si>
+    <t>赌场材料-120级</t>
+  </si>
+  <si>
+    <t>274_1023003|443_1023004|443_1023005|137_1023103|221_1023104|221_1023105|69_1023103|111_1023104|111_1023105|23_1023203|37_1023204|37_1023205|11_1023403|18_1023404|18_1023405|11_1023301|18_1023301|18_1023301</t>
+  </si>
+  <si>
+    <t>赌场材料-130级</t>
+  </si>
+  <si>
+    <t>227_1023004|906_1023005|113_1023104|453_1023105|57_1023104|227_1023105|19_1023204|76_1023205|9_1023404|38_1023405|9_1023301|38_1023301</t>
+  </si>
+  <si>
+    <t>赌场材料-140级</t>
+  </si>
+  <si>
+    <t>230_1023004|460_1023005|115_1023104|230_1023105|58_1023104|115_1023105|19_1023204|38_1023205|10_1023404|19_1023405|10_1023301|19_1023301</t>
+  </si>
+  <si>
+    <t>赌场材料-150级</t>
+  </si>
+  <si>
+    <t>532_1023005|266_1023105|133_1023105|44_1023205|22_1023405|22_1023301</t>
   </si>
 </sst>
 </file>
@@ -321,12 +393,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -647,7 +725,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -671,16 +749,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -689,91 +767,94 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1088,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -1447,6 +1528,138 @@
         <v>42</v>
       </c>
     </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="1">
+        <v>20010040</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1">
+        <v>20010050</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1">
+        <v>20010060</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="1">
+        <v>20010070</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="1">
+        <v>20010080</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1">
+        <v>20010090</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1">
+        <v>20010100</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="1">
+        <v>20010110</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="1">
+        <v>20010120</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1">
+        <v>20010130</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1">
+        <v>20010140</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1">
+        <v>20010150</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/dropDetailed.xlsx
+++ b/poker/resources/sample/dropDetailed.xlsx
@@ -161,73 +161,73 @@
     <t>赌场材料-40级</t>
   </si>
   <si>
-    <t>1434_1023001|717_1023101|359_1023101|120_1023201|60_1023401|60_1023301</t>
+    <t>1434_1023001_1|717_1023101_1|359_1023101_1|120_1023201_1|60_1023401_1|60_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-50级</t>
   </si>
   <si>
-    <t>1447_1023001|724_1023101|362_1023101|121_1023201|60_1023401|60_1023301</t>
+    <t>1447_1023001_1|724_1023101_1|362_1023101_1|121_1023201_1|60_1023401_1|60_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-60级</t>
   </si>
   <si>
-    <t>968_1023001|812_1023002|484_1023101|406_1023102|242_1023101|203_1023102|81_1023201|68_1023202|40_1023401|34_1023402|40_1023301|34_1023301</t>
+    <t>968_1023001_1|812_1023002_1|484_1023101_1|406_1023102_1|242_1023101_1|203_1023102_1|81_1023201_1|68_1023202_1|40_1023401_1|34_1023402_1|40_1023301_1|34_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-70级</t>
   </si>
   <si>
-    <t>265_1023001|889_1023002|133_1023101|445_1023102|66_1023101|222_1023102|22_1023201|74_1023202|11_1023401|37_1023402|11_1023301|37_1023301</t>
+    <t>265_1023001_1|889_1023002_1|133_1023101_1|445_1023102_1|66_1023101_1|222_1023102_1|22_1023201_1|74_1023202_1|11_1023401_1|37_1023402_1|11_1023301_1|37_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-80级</t>
   </si>
   <si>
-    <t>365_1023001|613_1023002|613_1023003|183_1023101|306_1023102|306_1023103|91_1023101|153_1023102|153_1023103|30_1023201|51_1023202|51_1023203|15_1023401|26_1023402|26_1023403|15_1023301|26_1023301|26_1023301</t>
+    <t>365_1023001_1|613_1023002_1|613_1023003_1|183_1023101_1|306_1023102_1|306_1023103_1|91_1023101_1|153_1023102_1|153_1023103_1|30_1023201_1|51_1023202_1|51_1023203_1|15_1023401_1|26_1023402_1|26_1023403_1|15_1023301_1|26_1023301_1|26_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-90级</t>
   </si>
   <si>
-    <t>223_1023002|893_1023003|112_1023102|447_1023103|56_1023102|223_1023103|19_1023202|74_1023203|9_1023402|37_1023403|9_1023301|37_1023301</t>
+    <t>223_1023002_1|893_1023003_1|112_1023102_1|447_1023103_1|56_1023102_1|223_1023103_1|19_1023202_1|74_1023203_1|9_1023402_1|37_1023403_1|9_1023301_1|37_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-100级</t>
   </si>
   <si>
-    <t>246_1023002|492_1023003|397_1023004|123_1023102|246_1023103|199_1023104|61_1023102|123_1023103|99_1023104|20_1023202|41_1023203|33_1023204|10_1023402|20_1023403|17_1023404|10_1023301|20_1023301|17_1023301</t>
+    <t>246_1023002_1|492_1023003_1|397_1023004_1|123_1023102_1|246_1023103_1|199_1023104_1|61_1023102_1|123_1023103_1|99_1023104_1|20_1023202_1|41_1023203_1|33_1023204_1|10_1023402_1|20_1023403_1|17_1023404_1|10_1023301_1|20_1023301_1|17_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-110级</t>
   </si>
   <si>
-    <t>264_1023003|853_1023004|132_1023103|427_1023104|66_1023103|213_1023104|22_1023203|71_1023204|11_1023403|36_1023404|11_1023301|36_1023301</t>
+    <t>264_1023003_1|853_1023004_1|132_1023103_1|427_1023104_1|66_1023103_1|213_1023104_1|22_1023203_1|71_1023204_1|11_1023403_1|36_1023404_1|11_1023301_1|36_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-120级</t>
   </si>
   <si>
-    <t>274_1023003|443_1023004|443_1023005|137_1023103|221_1023104|221_1023105|69_1023103|111_1023104|111_1023105|23_1023203|37_1023204|37_1023205|11_1023403|18_1023404|18_1023405|11_1023301|18_1023301|18_1023301</t>
+    <t>274_1023003_1|443_1023004_1|443_1023005_1|137_1023103_1|221_1023104_1|221_1023105_1|69_1023103_1|111_1023104_1|111_1023105_1|23_1023203_1|37_1023204_1|37_1023205_1|11_1023403_1|18_1023404_1|18_1023405_1|11_1023301_1|18_1023301_1|18_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-130级</t>
   </si>
   <si>
-    <t>227_1023004|906_1023005|113_1023104|453_1023105|57_1023104|227_1023105|19_1023204|76_1023205|9_1023404|38_1023405|9_1023301|38_1023301</t>
+    <t>227_1023004_1|906_1023005_1|113_1023104_1|453_1023105_1|57_1023104_1|227_1023105_1|19_1023204_1|76_1023205_1|9_1023404_1|38_1023405_1|9_1023301_1|38_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-140级</t>
   </si>
   <si>
-    <t>230_1023004|460_1023005|115_1023104|230_1023105|58_1023104|115_1023105|19_1023204|38_1023205|10_1023404|19_1023405|10_1023301|19_1023301</t>
+    <t>230_1023004_1|460_1023005_1|115_1023104_1|230_1023105_1|58_1023104_1|115_1023105_1|19_1023204_1|38_1023205_1|10_1023404_1|19_1023405_1|10_1023301_1|19_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-150级</t>
   </si>
   <si>
-    <t>532_1023005|266_1023105|133_1023105|44_1023205|22_1023405|22_1023301</t>
+    <t>532_1023005_1|266_1023105_1|133_1023105_1|44_1023205_1|22_1023405_1|22_1023301_1</t>
   </si>
 </sst>
 </file>

--- a/poker/resources/sample/dropDetailed.xlsx
+++ b/poker/resources/sample/dropDetailed.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="81">
   <si>
     <t>掉落ID</t>
   </si>
@@ -113,24 +113,6 @@
     <t>900_1990000_500000</t>
   </si>
   <si>
-    <t>普通-赌场材料随机1个</t>
-  </si>
-  <si>
-    <t>1200_1023001_1|600_1023002_1|140_1023003_1|50_1023004_1|10_1023005_1|1200_1023101_1|600_1023102_1|140_1023103_1|50_1023104_1|10_1023105_1|1200_1023201_1|600_1023202_1|140_1023203_1|50_1023204_1|10_1023205_1|1200_1023301_1|600_1023302_1|140_1023303_1|50_1023304_1|10_1023305_1|1200_1023401_1|600_1023402_1|140_1023403_1|50_1023404_1|10_1023405_1</t>
-  </si>
-  <si>
-    <t>豪华-赌场材料随机1个</t>
-  </si>
-  <si>
-    <t>780_1023001_1|900_1023002_1|200_1023003_1|100_1023004_1|20_1023005_1|780_1023101_1|900_1023102_1|200_1023103_1|100_1023104_1|20_1023105_1|780_1023201_1|900_1023202_1|200_1023203_1|100_1023204_1|20_1023205_1|780_1023301_1|900_1023302_1|200_1023303_1|100_1023304_1|20_1023305_1|780_1023401_1|900_1023402_1|200_1023403_1|100_1023404_1|20_1023405_1</t>
-  </si>
-  <si>
-    <t>尊贵-赌场材料随机1个</t>
-  </si>
-  <si>
-    <t>300_1023001_1|300_1023002_1|400_1023003_1|500_1023004_1|500_1023005_1|300_1023101_1|300_1023102_1|400_1023103_1|500_1023104_1|500_1023105_1|300_1023201_1|300_1023202_1|400_1023203_1|500_1023204_1|500_1023205_1|300_1023301_1|300_1023302_1|400_1023303_1|500_1023304_1|500_1023305_1|300_1023401_1|300_1023402_1|400_1023403_1|500_1023404_1|500_1023405_1</t>
-  </si>
-  <si>
     <t>拼图碎片包1</t>
   </si>
   <si>
@@ -161,73 +143,133 @@
     <t>赌场材料-40级</t>
   </si>
   <si>
-    <t>1434_1023001_1|717_1023101_1|359_1023101_1|120_1023201_1|60_1023401_1|60_1023301_1</t>
+    <t>1516_1023001_1|758_1023101_1|758_1023101_1|126_1023201_1|63_1023401_1|63_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-50级</t>
   </si>
   <si>
-    <t>1447_1023001_1|724_1023101_1|362_1023101_1|121_1023201_1|60_1023401_1|60_1023301_1</t>
+    <t>1509_1023001_1|755_1023101_1|755_1023101_1|126_1023201_1|63_1023401_1|63_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-60级</t>
   </si>
   <si>
-    <t>968_1023001_1|812_1023002_1|484_1023101_1|406_1023102_1|242_1023101_1|203_1023102_1|81_1023201_1|68_1023202_1|40_1023401_1|34_1023402_1|40_1023301_1|34_1023301_1</t>
+    <t>1005_1023001_1|843_1023002_1|502_1023101_1|421_1023102_1|502_1023101_1|421_1023102_1|84_1023201_1|70_1023202_1|42_1023401_1|35_1023402_1|42_1023301_1|35_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-70级</t>
   </si>
   <si>
-    <t>265_1023001_1|889_1023002_1|133_1023101_1|445_1023102_1|66_1023101_1|222_1023102_1|22_1023201_1|74_1023202_1|11_1023401_1|37_1023402_1|11_1023301_1|37_1023301_1</t>
+    <t>273_1023001_1|917_1023002_1|137_1023101_1|459_1023102_1|137_1023101_1|459_1023102_1|23_1023201_1|76_1023202_1|11_1023401_1|38_1023402_1|11_1023301_1|38_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-80级</t>
   </si>
   <si>
-    <t>365_1023001_1|613_1023002_1|613_1023003_1|183_1023101_1|306_1023102_1|306_1023103_1|91_1023101_1|153_1023102_1|153_1023103_1|30_1023201_1|51_1023202_1|51_1023203_1|15_1023401_1|26_1023402_1|26_1023403_1|15_1023301_1|26_1023301_1|26_1023301_1</t>
+    <t>376_1023001_1|630_1023002_1|630_1023003_1|188_1023101_1|315_1023102_1|315_1023103_1|188_1023101_1|315_1023102_1|315_1023103_1|31_1023201_1|52_1023202_1|52_1023203_1|16_1023401_1|26_1023402_1|26_1023403_1|16_1023301_1|26_1023301_1|26_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-90级</t>
   </si>
   <si>
-    <t>223_1023002_1|893_1023003_1|112_1023102_1|447_1023103_1|56_1023102_1|223_1023103_1|19_1023202_1|74_1023203_1|9_1023402_1|37_1023403_1|9_1023301_1|37_1023301_1</t>
+    <t>229_1023002_1|915_1023003_1|114_1023102_1|457_1023103_1|114_1023102_1|457_1023103_1|19_1023202_1|76_1023203_1|10_1023402_1|38_1023403_1|10_1023301_1|38_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-100级</t>
   </si>
   <si>
-    <t>246_1023002_1|492_1023003_1|397_1023004_1|123_1023102_1|246_1023103_1|199_1023104_1|61_1023102_1|123_1023103_1|99_1023104_1|20_1023202_1|41_1023203_1|33_1023204_1|10_1023402_1|20_1023403_1|17_1023404_1|10_1023301_1|20_1023301_1|17_1023301_1</t>
+    <t>251_1023002_1|503_1023003_1|406_1023004_1|126_1023102_1|251_1023103_1|203_1023104_1|126_1023102_1|251_1023103_1|203_1023104_1|21_1023202_1|42_1023203_1|34_1023204_1|10_1023402_1|21_1023403_1|17_1023404_1|10_1023301_1|21_1023301_1|17_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-110级</t>
   </si>
   <si>
-    <t>264_1023003_1|853_1023004_1|132_1023103_1|427_1023104_1|66_1023103_1|213_1023104_1|22_1023203_1|71_1023204_1|11_1023403_1|36_1023404_1|11_1023301_1|36_1023301_1</t>
+    <t>269_1023003_1|870_1023004_1|135_1023103_1|435_1023104_1|135_1023103_1|435_1023104_1|22_1023203_1|72_1023204_1|11_1023403_1|36_1023404_1|11_1023301_1|36_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-120级</t>
   </si>
   <si>
-    <t>274_1023003_1|443_1023004_1|443_1023005_1|137_1023103_1|221_1023104_1|221_1023105_1|69_1023103_1|111_1023104_1|111_1023105_1|23_1023203_1|37_1023204_1|37_1023205_1|11_1023403_1|18_1023404_1|18_1023405_1|11_1023301_1|18_1023301_1|18_1023301_1</t>
+    <t>279_1023003_1|451_1023004_1|451_1023005_1|139_1023103_1|225_1023104_1|225_1023105_1|139_1023103_1|225_1023104_1|225_1023105_1|23_1023203_1|38_1023204_1|38_1023205_1|12_1023403_1|19_1023404_1|19_1023405_1|12_1023301_1|19_1023301_1|19_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-130级</t>
   </si>
   <si>
-    <t>227_1023004_1|906_1023005_1|113_1023104_1|453_1023105_1|57_1023104_1|227_1023105_1|19_1023204_1|76_1023205_1|9_1023404_1|38_1023405_1|9_1023301_1|38_1023301_1</t>
+    <t>230_1023004_1|921_1023005_1|115_1023104_1|461_1023105_1|115_1023104_1|461_1023105_1|19_1023204_1|77_1023205_1|10_1023404_1|38_1023405_1|10_1023301_1|38_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-140级</t>
   </si>
   <si>
-    <t>230_1023004_1|460_1023005_1|115_1023104_1|230_1023105_1|58_1023104_1|115_1023105_1|19_1023204_1|38_1023205_1|10_1023404_1|19_1023405_1|10_1023301_1|19_1023301_1</t>
+    <t>234_1023004_1|468_1023005_1|117_1023104_1|234_1023105_1|117_1023104_1|234_1023105_1|19_1023204_1|39_1023205_1|10_1023404_1|19_1023405_1|10_1023301_1|19_1023301_1</t>
   </si>
   <si>
     <t>赌场材料-150级</t>
   </si>
   <si>
-    <t>532_1023005_1|266_1023105_1|133_1023105_1|44_1023205_1|22_1023405_1|22_1023301_1</t>
+    <t>540_1023005_1|270_1023105_1|270_1023105_1|45_1023205_1|23_1023405_1|23_1023301_1</t>
+  </si>
+  <si>
+    <t>1星材料包</t>
+  </si>
+  <si>
+    <t>4450_1023001_4|2960_1023101_2|1480_1023201_1|740_1023301_1|370_1023401_1</t>
+  </si>
+  <si>
+    <t>2星材料包</t>
+  </si>
+  <si>
+    <t>4450_1023002_4|2960_1023102_2|1480_1023202_1|740_1023302_1|370_1023402_1</t>
+  </si>
+  <si>
+    <t>3星材料包</t>
+  </si>
+  <si>
+    <t>4450_1023003_4|2960_1023103_2|1480_1023203_1|740_1023303_1|370_1023403_1</t>
+  </si>
+  <si>
+    <t>4星材料包</t>
+  </si>
+  <si>
+    <t>4450_1023004_4|2960_1023104_2|1480_1023204_1|740_1023304_1|370_1023404_1</t>
+  </si>
+  <si>
+    <t>5星材料包</t>
+  </si>
+  <si>
+    <t>4450_1023005_4|2960_1023105_2|1480_1023205_1|740_1023305_1|370_1023405_1</t>
+  </si>
+  <si>
+    <t>1星材料包X2</t>
+  </si>
+  <si>
+    <t>4450_1023001_8|2960_1023101_4|1480_1023201_2|740_1023301_2|370_1023401_2</t>
+  </si>
+  <si>
+    <t>2星材料包X2</t>
+  </si>
+  <si>
+    <t>4450_1023002_8|2960_1023102_4|1480_1023202_2|740_1023302_2|370_1023402_2</t>
+  </si>
+  <si>
+    <t>3星材料包X2</t>
+  </si>
+  <si>
+    <t>4450_1023003_8|2960_1023103_4|1480_1023203_2|740_1023303_2|370_1023403_2</t>
+  </si>
+  <si>
+    <t>4星材料包X2</t>
+  </si>
+  <si>
+    <t>4450_1023004_8|2960_1023104_4|1480_1023204_2|740_1023304_2|370_1023404_2</t>
+  </si>
+  <si>
+    <t>5星材料包X2</t>
+  </si>
+  <si>
+    <t>4450_1023005_8|2960_1023105_4|1480_1023205_2|740_1023305_2|370_1023405_2</t>
   </si>
 </sst>
 </file>
@@ -1169,10 +1211,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.375"/>
+    <col min="1" max="1" width="10.375"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="39.375" customWidth="1"/>
     <col min="4" max="4" width="19.375" customWidth="1"/>
@@ -1431,7 +1473,7 @@
     </row>
     <row r="10" customFormat="1" spans="1:3">
       <c r="A10">
-        <v>20000005</v>
+        <v>20000008</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -1442,86 +1484,86 @@
     </row>
     <row r="11" customFormat="1" spans="1:3">
       <c r="A11">
-        <v>20000006</v>
+        <v>20000009</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:3">
       <c r="A12">
-        <v>20000007</v>
+        <v>20000010</v>
       </c>
       <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
         <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:3">
       <c r="A13">
-        <v>20000008</v>
+        <v>20000011</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:3">
       <c r="A14">
-        <v>20000009</v>
+        <v>20000012</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:3">
       <c r="A15">
-        <v>20000010</v>
+        <v>20000021</v>
       </c>
       <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1">
+        <v>20010040</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:3">
-      <c r="A16">
-        <v>20000011</v>
-      </c>
-      <c r="B16" t="s">
-        <v>39</v>
       </c>
       <c r="C16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:3">
-      <c r="A17">
-        <v>20000012</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" s="1">
+        <v>20010050</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
         <v>40</v>
       </c>
-      <c r="C17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" spans="1:3">
-      <c r="A18">
-        <v>20000021</v>
-      </c>
-      <c r="B18" t="s">
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1">
+        <v>20010060</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C18" t="s">
@@ -1530,7 +1572,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1">
-        <v>20010040</v>
+        <v>20010070</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>43</v>
@@ -1541,7 +1583,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1">
-        <v>20010050</v>
+        <v>20010080</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>45</v>
@@ -1552,7 +1594,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1">
-        <v>20010060</v>
+        <v>20010090</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>47</v>
@@ -1563,7 +1605,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1">
-        <v>20010070</v>
+        <v>20010100</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>49</v>
@@ -1574,7 +1616,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1">
-        <v>20010080</v>
+        <v>20010110</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>51</v>
@@ -1585,7 +1627,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1">
-        <v>20010090</v>
+        <v>20010120</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>53</v>
@@ -1596,7 +1638,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1">
-        <v>20010100</v>
+        <v>20010130</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>55</v>
@@ -1607,7 +1649,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1">
-        <v>20010110</v>
+        <v>20010140</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>57</v>
@@ -1618,7 +1660,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1">
-        <v>20010120</v>
+        <v>20010150</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>59</v>
@@ -1627,37 +1669,114 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="1">
-        <v>20010130</v>
-      </c>
-      <c r="B28" s="1" t="s">
+    <row r="28" customFormat="1" spans="1:3">
+      <c r="A28">
+        <v>20020001</v>
+      </c>
+      <c r="B28" t="s">
         <v>61</v>
       </c>
       <c r="C28" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1">
-        <v>20010140</v>
-      </c>
-      <c r="B29" s="1" t="s">
+    <row r="29" customFormat="1" spans="1:3">
+      <c r="A29">
+        <v>20020002</v>
+      </c>
+      <c r="B29" t="s">
         <v>63</v>
       </c>
       <c r="C29" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="1">
-        <v>20010150</v>
-      </c>
-      <c r="B30" s="1" t="s">
+    <row r="30" customFormat="1" spans="1:3">
+      <c r="A30">
+        <v>20020003</v>
+      </c>
+      <c r="B30" t="s">
         <v>65</v>
       </c>
       <c r="C30" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>20020004</v>
+      </c>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>20020005</v>
+      </c>
+      <c r="B32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:3">
+      <c r="A33">
+        <v>20020011</v>
+      </c>
+      <c r="B33" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:3">
+      <c r="A34">
+        <v>20020012</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:3">
+      <c r="A35">
+        <v>20020013</v>
+      </c>
+      <c r="B35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:3">
+      <c r="A36">
+        <v>20020014</v>
+      </c>
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:3">
+      <c r="A37">
+        <v>20020015</v>
+      </c>
+      <c r="B37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/dropDetailed.xlsx
+++ b/poker/resources/sample/dropDetailed.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="78">
   <si>
     <t>掉落ID</t>
   </si>
@@ -143,73 +143,64 @@
     <t>赌场材料-40级</t>
   </si>
   <si>
-    <t>1516_1023001_1|758_1023101_1|758_1023101_1|126_1023201_1|63_1023401_1|63_1023301_1</t>
+    <t>2500_1023001_1|833_1023101_1|208_1023201_1|104_1023301_1|52_1023401_1</t>
   </si>
   <si>
     <t>赌场材料-50级</t>
   </si>
   <si>
-    <t>1509_1023001_1|755_1023101_1|755_1023101_1|126_1023201_1|63_1023401_1|63_1023301_1</t>
-  </si>
-  <si>
     <t>赌场材料-60级</t>
   </si>
   <si>
-    <t>1005_1023001_1|843_1023002_1|502_1023101_1|421_1023102_1|502_1023101_1|421_1023102_1|84_1023201_1|70_1023202_1|42_1023401_1|35_1023402_1|42_1023301_1|35_1023301_1</t>
+    <t>2500_1023001_1|1667_1023002_1|833_1023101_1|556_1023102_1|208_1023201_1|139_1023202_1|104_1023301_1|69_1023302_1|52_1023401_1|35_1023402_1</t>
   </si>
   <si>
     <t>赌场材料-70级</t>
   </si>
   <si>
-    <t>273_1023001_1|917_1023002_1|137_1023101_1|459_1023102_1|137_1023101_1|459_1023102_1|23_1023201_1|76_1023202_1|11_1023401_1|38_1023402_1|11_1023301_1|38_1023301_1</t>
-  </si>
-  <si>
     <t>赌场材料-80级</t>
   </si>
   <si>
-    <t>376_1023001_1|630_1023002_1|630_1023003_1|188_1023101_1|315_1023102_1|315_1023103_1|188_1023101_1|315_1023102_1|315_1023103_1|31_1023201_1|52_1023202_1|52_1023203_1|16_1023401_1|26_1023402_1|26_1023403_1|16_1023301_1|26_1023301_1|26_1023301_1</t>
+    <t>2500_1023001_1|1667_1023002_1|1250_1023003_1|833_1023101_1|556_1023102_1|417_1023103_1|208_1023201_1|139_1023202_1|104_1023203_1|104_1023301_1|69_1023302_1|52_1023303_1|52_1023401_1|35_1023402_1|26_1023403_1</t>
   </si>
   <si>
     <t>赌场材料-90级</t>
   </si>
   <si>
-    <t>229_1023002_1|915_1023003_1|114_1023102_1|457_1023103_1|114_1023102_1|457_1023103_1|19_1023202_1|76_1023203_1|10_1023402_1|38_1023403_1|10_1023301_1|38_1023301_1</t>
+    <t>250_1023001_1|1667_1023002_1|1250_1023003_1|83_1023101_1|556_1023102_1|417_1023103_1|20_1023201_1|139_1023202_1|104_1023203_1|10_1023301_1|69_1023302_1|52_1023303_1|5_1023401_1|35_1023402_1|26_1023403_1</t>
   </si>
   <si>
     <t>赌场材料-100级</t>
   </si>
   <si>
-    <t>251_1023002_1|503_1023003_1|406_1023004_1|126_1023102_1|251_1023103_1|203_1023104_1|126_1023102_1|251_1023103_1|203_1023104_1|21_1023202_1|42_1023203_1|34_1023204_1|10_1023402_1|21_1023403_1|17_1023404_1|10_1023301_1|21_1023301_1|17_1023301_1</t>
+    <t>250_1023001_1|1667_1023002_1|1250_1023003_1|833_1023004_1|83_1023101_1|556_1023102_1|417_1023103_1|278_1023104_1|20_1023201_1|139_1023202_1|104_1023203_1|69_1023204_1|10_1023301_1|69_1023302_1|52_1023303_1|35_1023304_1|5_1023401_1|35_1023402_1|26_1023403_1|17_1023404_1</t>
   </si>
   <si>
     <t>赌场材料-110级</t>
   </si>
   <si>
-    <t>269_1023003_1|870_1023004_1|135_1023103_1|435_1023104_1|135_1023103_1|435_1023104_1|22_1023203_1|72_1023204_1|11_1023403_1|36_1023404_1|11_1023301_1|36_1023301_1</t>
+    <t>250_1023001_1|166_1023002_1|1250_1023003_1|833_1023004_1|83_1023101_1|55_1023102_1|417_1023103_1|278_1023104_1|20_1023201_1|13_1023202_1|104_1023203_1|69_1023204_1|10_1023301_1|6_1023302_1|52_1023303_1|35_1023304_1|5_1023401_1|3_1023402_1|26_1023403_1|17_1023404_1</t>
   </si>
   <si>
     <t>赌场材料-120级</t>
   </si>
   <si>
-    <t>279_1023003_1|451_1023004_1|451_1023005_1|139_1023103_1|225_1023104_1|225_1023105_1|139_1023103_1|225_1023104_1|225_1023105_1|23_1023203_1|38_1023204_1|38_1023205_1|12_1023403_1|19_1023404_1|19_1023405_1|12_1023301_1|19_1023301_1|19_1023301_1</t>
+    <t>250_1023001_1|166_1023002_1|1250_1023003_1|833_1023004_1|417_1023005_1|83_1023101_1|55_1023102_1|417_1023103_1|278_1023104_1|139_1023105_1|20_1023201_1|13_1023202_1|104_1023203_1|69_1023204_1|35_1023205_1|10_1023301_1|6_1023302_1|52_1023303_1|35_1023304_1|17_1023305_1|5_1023401_1|3_1023402_1|26_1023403_1|17_1023404_1|9_1023405_1</t>
   </si>
   <si>
     <t>赌场材料-130级</t>
   </si>
   <si>
-    <t>230_1023004_1|921_1023005_1|115_1023104_1|461_1023105_1|115_1023104_1|461_1023105_1|19_1023204_1|77_1023205_1|10_1023404_1|38_1023405_1|10_1023301_1|38_1023301_1</t>
+    <t>250_1023001_1|166_1023002_1|125_1023003_1|833_1023004_1|417_1023005_1|83_1023101_1|55_1023102_1|41_1023103_1|278_1023104_1|139_1023105_1|20_1023201_1|13_1023202_1|10_1023203_1|69_1023204_1|35_1023205_1|10_1023301_1|6_1023302_1|5_1023303_1|35_1023304_1|17_1023305_1|5_1023401_1|3_1023402_1|2_1023403_1|17_1023404_1|9_1023405_1</t>
   </si>
   <si>
     <t>赌场材料-140级</t>
   </si>
   <si>
-    <t>234_1023004_1|468_1023005_1|117_1023104_1|234_1023105_1|117_1023104_1|234_1023105_1|19_1023204_1|39_1023205_1|10_1023404_1|19_1023405_1|10_1023301_1|19_1023301_1</t>
-  </si>
-  <si>
     <t>赌场材料-150级</t>
   </si>
   <si>
-    <t>540_1023005_1|270_1023105_1|270_1023105_1|45_1023205_1|23_1023405_1|23_1023301_1</t>
+    <t>250_1023001_1|166_1023002_1|125_1023003_1|83_1023004_1|417_1023005_1|83_1023101_1|55_1023102_1|41_1023103_1|27_1023104_1|139_1023105_1|20_1023201_1|13_1023202_1|10_1023203_1|6_1023204_1|35_1023205_1|10_1023301_1|6_1023302_1|5_1023303_1|3_1023304_1|17_1023305_1|5_1023401_1|3_1023402_1|2_1023403_1|1_1023404_1|9_1023405_1</t>
   </si>
   <si>
     <t>1星材料包</t>
@@ -1556,7 +1547,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1564,10 +1555,10 @@
         <v>20010060</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
         <v>41</v>
-      </c>
-      <c r="C18" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1575,10 +1566,10 @@
         <v>20010070</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1586,10 +1577,10 @@
         <v>20010080</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1597,10 +1588,10 @@
         <v>20010090</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1608,10 +1599,10 @@
         <v>20010100</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1619,10 +1610,10 @@
         <v>20010110</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1630,10 +1621,10 @@
         <v>20010120</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1641,10 +1632,10 @@
         <v>20010130</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1652,10 +1643,10 @@
         <v>20010140</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1663,10 +1654,10 @@
         <v>20010150</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:3">
@@ -1674,10 +1665,10 @@
         <v>20020001</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:3">
@@ -1685,10 +1676,10 @@
         <v>20020002</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:3">
@@ -1696,10 +1687,10 @@
         <v>20020003</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1707,10 +1698,10 @@
         <v>20020004</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1718,10 +1709,10 @@
         <v>20020005</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:3">
@@ -1729,10 +1720,10 @@
         <v>20020011</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:3">
@@ -1740,10 +1731,10 @@
         <v>20020012</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:3">
@@ -1751,10 +1742,10 @@
         <v>20020013</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:3">
@@ -1762,10 +1753,10 @@
         <v>20020014</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:3">
@@ -1773,10 +1764,10 @@
         <v>20020015</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/dropDetailed.xlsx
+++ b/poker/resources/sample/dropDetailed.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="105">
   <si>
     <t>掉落ID</t>
   </si>
@@ -168,64 +168,73 @@
     <t>赌场材料-40级</t>
   </si>
   <si>
-    <t>2500_1023001_1|833_1023101_1|208_1023201_1|104_1023301_1|52_1023401_1</t>
+    <t>3790_1023001_1|1061_1023101_1|352_1023201_1|189_1023301_1|107_1023401_1</t>
   </si>
   <si>
     <t>赌场材料-50级</t>
   </si>
   <si>
+    <t>3772_1023001_1|1057_1023101_1|352_1023201_1|189_1023301_1|107_1023401_1</t>
+  </si>
+  <si>
     <t>赌场材料-60级</t>
   </si>
   <si>
-    <t>2500_1023001_1|833_1023001_2|833_1023101_1|278_1023101_2|208_1023201_1|69_1023201_2|104_1023301_1|34_1023301_2|52_1023401_1|17_1023401_2</t>
+    <t>2512_1023001_1|1686_1023001_5|702_1023101_1|505_1023101_5|235_1023201_1|196_1023201_5|231_1023301_1|71_1023401_1|56_1023401_5</t>
   </si>
   <si>
     <t>赌场材料-70级</t>
   </si>
   <si>
+    <t>682_1023001_1|1834_1023001_5|191_1023101_1|550_1023101_5|64_1023201_1|212_1023201_5|33_1023301_1|163_1023301_5|18_1023401_1|60_1023401_5</t>
+  </si>
+  <si>
     <t>赌场材料-80级</t>
   </si>
   <si>
-    <t>2500_1023001_1|833_1023001_2|625_1023001_2|833_1023101_1|278_1023101_2|208_1023101_2|208_1023201_1|69_1023201_2|52_1023201_2|104_1023301_1|34_1023301_2|26_1023301_2|52_1023401_1|17_1023401_2|13_1023401_2</t>
+    <t>940_1023001_1|1260_1023001_5|1260_1023001_17|263_1023101_1|378_1023101_5|378_1023101_16|86_1023201_1|145_1023201_5|145_1023201_15|48_1023301_1|111_1023301_5|88_1023301_15|27_1023401_1|41_1023401_5|41_1023401_15</t>
   </si>
   <si>
     <t>赌场材料-90级</t>
   </si>
   <si>
-    <t>250_1023001_1|833_1023001_2|625_1023001_2|83_1023101_1|278_1023101_2|208_1023101_2|20_1023201_1|69_1023201_2|52_1023201_2|10_1023301_1|34_1023301_2|26_1023301_2|5_1023401_1|17_1023401_2|13_1023401_2</t>
+    <t>458_1023001_5|1830_1023001_17|136_1023101_5|548_1023101_16|53_1023201_5|212_1023201_15|43_1023301_5|129_1023301_15|16_1023401_5|60_1023401_15</t>
   </si>
   <si>
     <t>赌场材料-100级</t>
   </si>
   <si>
-    <t>250_1023001_1|833_1023001_2|625_1023001_2|277_1023001_3|83_1023101_1|278_1023101_2|208_1023101_2|92_1023101_3|20_1023201_1|69_1023201_2|52_1023201_2|23_1023201_3|10_1023301_1|34_1023301_2|26_1023301_2</t>
+    <t>502_1023001_5|1006_1023001_17|609_1023001_50|151_1023101_5|301_1023101_16|162_1023101_47|58_1023201_5|117_1023201_15|57_1023201_46|43_1023301_5|71_1023301_15|34_1023301_46|16_1023401_5|33_1023401_15|17_1023401_46</t>
   </si>
   <si>
     <t>赌场材料-110级</t>
   </si>
   <si>
-    <t>250_1023001_1|83_1023001_2|625_1023001_2|277_1023001_3|83_1023101_1|27_1023101_2|208_1023101_2|92_1023101_3|20_1023201_1|6_1023201_2|52_1023201_2|23_1023201_3|10_1023301_1|3_1023301_2|26_1023301_2</t>
+    <t>538_1023001_17|1305_1023001_50|162_1023101_16|348_1023101_47|61_1023201_15|122_1023201_46|37_1023301_15|72_1023301_46|17_1023401_15|36_1023401_46</t>
   </si>
   <si>
     <t>赌场材料-120级</t>
   </si>
   <si>
-    <t>250_1023001_1|83_1023001_2|625_1023001_2|277_1023001_3|69_1023001_6|83_1023101_1|27_1023101_2|208_1023101_2|92_1023101_3|23_1023101_6|20_1023201_1|6_1023201_2|52_1023201_2|23_1023201_3|5_1023201_6</t>
+    <t>558_1023001_17|676_1023001_50|541_1023001_89|166_1023101_16|180_1023101_47|135_1023101_83|64_1023201_15|64_1023201_46|45_1023201_81|40_1023301_15|38_1023301_46|28_1023301_82|19_1023401_15|19_1023401_46|13_1023401_82</t>
   </si>
   <si>
     <t>赌场材料-130级</t>
   </si>
   <si>
-    <t>250_1023001_1|83_1023001_2|62_1023001_2|277_1023001_3|69_1023001_6|83_1023101_1|27_1023101_2|20_1023101_2|92_1023101_3|23_1023101_6|20_1023201_1|6_1023201_2|5_1023201_2|23_1023201_3|5_1023201_6</t>
+    <t>345_1023001_50|1105_1023001_89|92_1023101_47|276_1023101_83|32_1023201_46|92_1023201_81|20_1023301_46|57_1023301_82|10_1023401_46|26_1023401_82</t>
   </si>
   <si>
     <t>赌场材料-140级</t>
   </si>
   <si>
+    <t>351_1023001_50|561_1023001_89|93_1023101_47|140_1023101_83|32_1023201_46|46_1023201_81|20_1023301_46|28_1023301_82|10_1023401_46|13_1023401_82</t>
+  </si>
+  <si>
     <t>赌场材料-150级</t>
   </si>
   <si>
-    <t>250_1023001_1|83_1023001_2|62_1023001_2|27_1023001_3|69_1023001_6|83_1023101_1|27_1023101_2|20_1023101_2|9_1023101_3|23_1023101_6|20_1023201_1|6_1023201_2|5_1023201_2|2_1023201_3|5_1023201_6</t>
+    <t>648_1023001_89|162_1023101_83|54_1023201_81|34_1023301_82|16_1023401_82</t>
   </si>
   <si>
     <t>1星材料包</t>
@@ -277,6 +286,21 @@
   </si>
   <si>
     <t>4450_1023001_48|2960_1023101_24|1480_1023201_12|740_1023301_12|370_1023401_12</t>
+  </si>
+  <si>
+    <t>1星材料包-35</t>
+  </si>
+  <si>
+    <t>6566_1023001_35|1928_1023101_35|750_1023201_35|503_1023301_35|251_1023401_35</t>
+  </si>
+  <si>
+    <t>1星材料包-40</t>
+  </si>
+  <si>
+    <t>6566_1023001_40|1928_1023101_40|750_1023201_40|503_1023301_40|251_1023401_40</t>
+  </si>
+  <si>
+    <t>2500_1023001_1|833_1023101_1|208_1023201_1|104_1023301_1|52_1023401_1</t>
   </si>
   <si>
     <t>2500_1023001_1|1667_1023002_1|833_1023101_1|556_1023102_1|208_1023201_1|139_1023202_1|104_1023301_1|69_1023302_1|52_1023401_1|35_1023402_1</t>
@@ -508,7 +532,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -524,6 +548,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -846,7 +876,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -870,16 +900,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -888,90 +918,90 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -982,6 +1012,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1296,7 +1329,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -1641,7 +1674,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1649,10 +1682,10 @@
         <v>20010060</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1660,10 +1693,10 @@
         <v>20010070</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1671,10 +1704,10 @@
         <v>20010080</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1682,10 +1715,10 @@
         <v>20010090</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1693,10 +1726,10 @@
         <v>20010100</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1704,10 +1737,10 @@
         <v>20010110</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1715,10 +1748,10 @@
         <v>20010120</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1726,10 +1759,10 @@
         <v>20010130</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1737,10 +1770,10 @@
         <v>20010140</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1748,10 +1781,10 @@
         <v>20010150</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:3">
@@ -1759,10 +1792,10 @@
         <v>20020001</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:3">
@@ -1770,10 +1803,10 @@
         <v>20020002</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:3">
@@ -1781,10 +1814,10 @@
         <v>20020003</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1792,10 +1825,10 @@
         <v>20020004</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1803,10 +1836,10 @@
         <v>20020005</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:3">
@@ -1814,10 +1847,10 @@
         <v>20020011</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:3">
@@ -1825,10 +1858,10 @@
         <v>20020012</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:3">
@@ -1836,10 +1869,10 @@
         <v>20020013</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:3">
@@ -1847,10 +1880,10 @@
         <v>20020014</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:3">
@@ -1858,10 +1891,32 @@
         <v>20020015</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:3">
+      <c r="A38" s="4">
+        <v>20020020</v>
+      </c>
+      <c r="B38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="4">
+        <v>20020021</v>
+      </c>
+      <c r="B39" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1887,7 +1942,7 @@
         <v>20010040</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="str">
         <f>_xlfn.XLOOKUP(A1,$A$16:$A$222,$L$16:$L$222,B1)</f>
@@ -1899,7 +1954,7 @@
         <v>20010050</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1" t="str">
         <f t="shared" ref="C2:C12" si="0">_xlfn.XLOOKUP(A2,$A$16:$A$222,$L$16:$L$222,B2)</f>
@@ -1911,7 +1966,7 @@
         <v>20010060</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1923,7 +1978,7 @@
         <v>20010070</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C4" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1935,7 +1990,7 @@
         <v>20010080</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C5" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1947,7 +2002,7 @@
         <v>20010090</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C6" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1959,7 +2014,7 @@
         <v>20010100</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C7" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1971,7 +2026,7 @@
         <v>20010110</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C8" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1983,7 +2038,7 @@
         <v>20010120</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C9" s="1" t="str">
         <f t="shared" si="0"/>
@@ -1995,7 +2050,7 @@
         <v>20010130</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C10" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2007,7 +2062,7 @@
         <v>20010140</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C11" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2019,7 +2074,7 @@
         <v>20010150</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C12" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2031,7 +2086,7 @@
         <v>20010060</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="L16" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,L17:L26)</f>
@@ -2474,7 +2529,7 @@
         <v>20010070</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="L29" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,L30:L44)</f>
@@ -2960,7 +3015,7 @@
         <v>20</v>
       </c>
       <c r="G49">
-        <f t="shared" ref="G49:G58" si="9">VALUE(D49)</f>
+        <f t="shared" ref="G49:G61" si="9">VALUE(D49)</f>
         <v>1023001</v>
       </c>
       <c r="H49">
@@ -2972,15 +3027,15 @@
         <v>20</v>
       </c>
       <c r="J49">
-        <f t="shared" ref="J49:J58" si="10">ROUNDUP(F49/I49,0)</f>
+        <f t="shared" ref="J49:J61" si="10">ROUNDUP(F49/I49,0)</f>
         <v>1</v>
       </c>
       <c r="K49">
-        <f t="shared" ref="K49:K58" si="11">ROUNDDOWN(C49/J49,0)</f>
+        <f t="shared" ref="K49:K61" si="11">ROUNDDOWN(C49/J49,0)</f>
         <v>2500</v>
       </c>
       <c r="L49" s="2" t="str">
-        <f t="shared" ref="L49:L58" si="12">_xlfn.TEXTJOIN("_",TRUE,K49,H49,J49)</f>
+        <f t="shared" ref="L49:L61" si="12">_xlfn.TEXTJOIN("_",TRUE,K49,H49,J49)</f>
         <v>2500_1023001_1</v>
       </c>
     </row>
@@ -3390,7 +3445,7 @@
         <v>720</v>
       </c>
       <c r="G59">
-        <f>VALUE(D59)</f>
+        <f t="shared" si="9"/>
         <v>1023302</v>
       </c>
       <c r="H59">
@@ -3402,15 +3457,15 @@
         <v>480</v>
       </c>
       <c r="J59">
-        <f>ROUNDUP(F59/I59,0)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="K59">
-        <f>ROUNDDOWN(C59/J59,0)</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="L59" s="2" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,K59,H59,J59)</f>
+        <f t="shared" si="12"/>
         <v>34_1023301_2</v>
       </c>
     </row>
@@ -3433,7 +3488,7 @@
         <v>960</v>
       </c>
       <c r="G60">
-        <f>VALUE(D60)</f>
+        <f t="shared" si="9"/>
         <v>1023303</v>
       </c>
       <c r="H60">
@@ -3445,15 +3500,15 @@
         <v>480</v>
       </c>
       <c r="J60">
-        <f>ROUNDUP(F60/I60,0)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="K60">
-        <f>ROUNDDOWN(C60/J60,0)</f>
+        <f t="shared" si="11"/>
         <v>26</v>
       </c>
       <c r="L60" s="2" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,K60,H60,J60)</f>
+        <f t="shared" si="12"/>
         <v>26_1023301_2</v>
       </c>
     </row>
@@ -3476,7 +3531,7 @@
         <v>960</v>
       </c>
       <c r="G61">
-        <f>VALUE(D61)</f>
+        <f t="shared" si="9"/>
         <v>1023401</v>
       </c>
       <c r="H61">
@@ -3488,15 +3543,15 @@
         <v>960</v>
       </c>
       <c r="J61">
-        <f>ROUNDUP(F61/I61,0)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K61">
-        <f>ROUNDDOWN(C61/J61,0)</f>
+        <f t="shared" si="11"/>
         <v>52</v>
       </c>
       <c r="L61" s="2" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,K61,H61,J61)</f>
+        <f t="shared" si="12"/>
         <v>52_1023401_1</v>
       </c>
     </row>
@@ -3586,8 +3641,6 @@
         <v>13_1023401_2</v>
       </c>
     </row>
-    <row r="64" customFormat="1"/>
-    <row r="65" customFormat="1"/>
     <row r="66" spans="1:12">
       <c r="A66">
         <v>20010090</v>
@@ -4247,8 +4300,6 @@
         <v>13_1023401_2</v>
       </c>
     </row>
-    <row r="82" customFormat="1"/>
-    <row r="83" customFormat="1"/>
     <row r="84" spans="1:12">
       <c r="A84">
         <v>20010100</v>
@@ -4282,7 +4333,7 @@
         <v>20</v>
       </c>
       <c r="G85">
-        <f t="shared" ref="G85:G99" si="17">VALUE(D85)</f>
+        <f t="shared" ref="G85:G102" si="17">VALUE(D85)</f>
         <v>1023001</v>
       </c>
       <c r="H85">
@@ -4294,15 +4345,15 @@
         <v>20</v>
       </c>
       <c r="J85">
-        <f t="shared" ref="J85:J99" si="18">ROUNDUP(F85/I85,0)</f>
+        <f t="shared" ref="J85:J102" si="18">ROUNDUP(F85/I85,0)</f>
         <v>1</v>
       </c>
       <c r="K85">
-        <f t="shared" ref="K85:K99" si="19">ROUNDDOWN(C85/J85,0)</f>
+        <f t="shared" ref="K85:K102" si="19">ROUNDDOWN(C85/J85,0)</f>
         <v>250</v>
       </c>
       <c r="L85" s="2" t="str">
-        <f t="shared" ref="L85:L99" si="20">_xlfn.TEXTJOIN("_",TRUE,K85,H85,J85)</f>
+        <f t="shared" ref="L85:L102" si="20">_xlfn.TEXTJOIN("_",TRUE,K85,H85,J85)</f>
         <v>250_1023001_1</v>
       </c>
     </row>
@@ -4927,7 +4978,7 @@
         <v>1440</v>
       </c>
       <c r="G100">
-        <f>VALUE(D100)</f>
+        <f t="shared" si="17"/>
         <v>1023304</v>
       </c>
       <c r="H100">
@@ -4939,15 +4990,15 @@
         <v>480</v>
       </c>
       <c r="J100">
-        <f>ROUNDUP(F100/I100,0)</f>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="K100">
-        <f>ROUNDDOWN(C100/J100,0)</f>
+        <f t="shared" si="19"/>
         <v>11</v>
       </c>
       <c r="L100" s="2" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,K100,H100,J100)</f>
+        <f t="shared" si="20"/>
         <v>11_1023301_3</v>
       </c>
     </row>
@@ -4970,7 +5021,7 @@
         <v>960</v>
       </c>
       <c r="G101">
-        <f>VALUE(D101)</f>
+        <f t="shared" si="17"/>
         <v>1023401</v>
       </c>
       <c r="H101">
@@ -4982,15 +5033,15 @@
         <v>960</v>
       </c>
       <c r="J101">
-        <f>ROUNDUP(F101/I101,0)</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="K101">
-        <f>ROUNDDOWN(C101/J101,0)</f>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="L101" s="2" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,K101,H101,J101)</f>
+        <f t="shared" si="20"/>
         <v>5_1023401_1</v>
       </c>
     </row>
@@ -5013,7 +5064,7 @@
         <v>1440</v>
       </c>
       <c r="G102">
-        <f>VALUE(D102)</f>
+        <f t="shared" si="17"/>
         <v>1023402</v>
       </c>
       <c r="H102">
@@ -5025,15 +5076,15 @@
         <v>960</v>
       </c>
       <c r="J102">
-        <f>ROUNDUP(F102/I102,0)</f>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="K102">
-        <f>ROUNDDOWN(C102/J102,0)</f>
+        <f t="shared" si="19"/>
         <v>17</v>
       </c>
       <c r="L102" s="2" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,K102,H102,J102)</f>
+        <f t="shared" si="20"/>
         <v>17_1023401_2</v>
       </c>
     </row>
@@ -5123,8 +5174,6 @@
         <v>5_1023401_3</v>
       </c>
     </row>
-    <row r="105" customFormat="1"/>
-    <row r="106" customFormat="1"/>
     <row r="107" spans="1:12">
       <c r="A107">
         <v>20010110</v>
@@ -5999,8 +6048,6 @@
         <v>5_1023401_3</v>
       </c>
     </row>
-    <row r="128" customFormat="1"/>
-    <row r="129" customFormat="1"/>
     <row r="130" spans="1:12">
       <c r="A130">
         <v>20010120</v>
@@ -6034,7 +6081,7 @@
         <v>20</v>
       </c>
       <c r="G131">
-        <f t="shared" ref="G131:G150" si="25">VALUE(D131)</f>
+        <f t="shared" ref="G131:G153" si="25">VALUE(D131)</f>
         <v>1023001</v>
       </c>
       <c r="H131">
@@ -6046,15 +6093,15 @@
         <v>20</v>
       </c>
       <c r="J131">
-        <f t="shared" ref="J131:J150" si="26">ROUNDUP(F131/I131,0)</f>
+        <f t="shared" ref="J131:J153" si="26">ROUNDUP(F131/I131,0)</f>
         <v>1</v>
       </c>
       <c r="K131">
-        <f t="shared" ref="K131:K150" si="27">ROUNDDOWN(C131/J131,0)</f>
+        <f t="shared" ref="K131:K153" si="27">ROUNDDOWN(C131/J131,0)</f>
         <v>250</v>
       </c>
       <c r="L131" s="2" t="str">
-        <f t="shared" ref="L131:L150" si="28">_xlfn.TEXTJOIN("_",TRUE,K131,H131,J131)</f>
+        <f t="shared" ref="L131:L153" si="28">_xlfn.TEXTJOIN("_",TRUE,K131,H131,J131)</f>
         <v>250_1023001_1</v>
       </c>
     </row>
@@ -6894,7 +6941,7 @@
         <v>960</v>
       </c>
       <c r="G151">
-        <f>VALUE(D151)</f>
+        <f t="shared" si="25"/>
         <v>1023401</v>
       </c>
       <c r="H151">
@@ -6906,15 +6953,15 @@
         <v>960</v>
       </c>
       <c r="J151">
-        <f>ROUNDUP(F151/I151,0)</f>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="K151">
-        <f>ROUNDDOWN(C151/J151,0)</f>
+        <f t="shared" si="27"/>
         <v>5</v>
       </c>
       <c r="L151" s="2" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,K151,H151,J151)</f>
+        <f t="shared" si="28"/>
         <v>5_1023401_1</v>
       </c>
     </row>
@@ -6937,7 +6984,7 @@
         <v>1440</v>
       </c>
       <c r="G152">
-        <f>VALUE(D152)</f>
+        <f t="shared" si="25"/>
         <v>1023402</v>
       </c>
       <c r="H152">
@@ -6949,15 +6996,15 @@
         <v>960</v>
       </c>
       <c r="J152">
-        <f>ROUNDUP(F152/I152,0)</f>
+        <f t="shared" si="26"/>
         <v>2</v>
       </c>
       <c r="K152">
-        <f>ROUNDDOWN(C152/J152,0)</f>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="L152" s="2" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,K152,H152,J152)</f>
+        <f t="shared" si="28"/>
         <v>1_1023401_2</v>
       </c>
     </row>
@@ -6980,7 +7027,7 @@
         <v>1920</v>
       </c>
       <c r="G153">
-        <f>VALUE(D153)</f>
+        <f t="shared" si="25"/>
         <v>1023403</v>
       </c>
       <c r="H153">
@@ -6992,15 +7039,15 @@
         <v>960</v>
       </c>
       <c r="J153">
-        <f>ROUNDUP(F153/I153,0)</f>
+        <f t="shared" si="26"/>
         <v>2</v>
       </c>
       <c r="K153">
-        <f>ROUNDDOWN(C153/J153,0)</f>
+        <f t="shared" si="27"/>
         <v>13</v>
       </c>
       <c r="L153" s="2" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,K153,H153,J153)</f>
+        <f t="shared" si="28"/>
         <v>13_1023401_2</v>
       </c>
     </row>
@@ -7090,8 +7137,6 @@
         <v>1_1023401_6</v>
       </c>
     </row>
-    <row r="156" customFormat="1"/>
-    <row r="157" customFormat="1"/>
     <row r="158" spans="1:12">
       <c r="A158">
         <v>20010130</v>
@@ -8181,8 +8226,6 @@
         <v>1_1023401_6</v>
       </c>
     </row>
-    <row r="184" customFormat="1"/>
-    <row r="185" customFormat="1"/>
     <row r="186" spans="1:12">
       <c r="A186">
         <v>20010140</v>
@@ -9272,8 +9315,6 @@
         <v>1_1023401_6</v>
       </c>
     </row>
-    <row r="212" customFormat="1"/>
-    <row r="213" customFormat="1"/>
     <row r="214" spans="1:12">
       <c r="A214">
         <v>20010150</v>
@@ -10385,7 +10426,7 @@
         <v>20020001</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="str">
         <f t="shared" ref="C1:C12" si="0">_xlfn.XLOOKUP(A1,$A$16:$A$222,$L$16:$L$222,B1)</f>
@@ -10397,7 +10438,7 @@
         <v>20020002</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C2" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10409,7 +10450,7 @@
         <v>20020003</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C3" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10421,7 +10462,7 @@
         <v>20020004</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C4" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10433,7 +10474,7 @@
         <v>20020005</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C5" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10445,7 +10486,7 @@
         <v>20020011</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10457,7 +10498,7 @@
         <v>20020012</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C7" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10469,7 +10510,7 @@
         <v>20020013</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C8" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10481,7 +10522,7 @@
         <v>20020014</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C9" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10493,7 +10534,7 @@
         <v>20020015</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C10" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10508,22 +10549,22 @@
     </row>
     <row r="15" spans="1:12">
       <c r="E15" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F15" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G15" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H15" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I15" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="J15" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -11309,8 +11350,6 @@
     <row r="63" customFormat="1" spans="2:12">
       <c r="L63" s="2"/>
     </row>
-    <row r="64" customFormat="1"/>
-    <row r="65" customFormat="1"/>
     <row r="66" spans="1:12">
       <c r="A66">
         <v>20020004</v>
@@ -11570,8 +11609,6 @@
     <row r="81" customFormat="1" spans="1:12">
       <c r="L81" s="2"/>
     </row>
-    <row r="82" customFormat="1"/>
-    <row r="83" customFormat="1"/>
     <row r="84" spans="1:12">
       <c r="A84">
         <v>20020005</v>
@@ -11846,8 +11883,6 @@
     <row r="104" spans="1:12">
       <c r="L104" s="2"/>
     </row>
-    <row r="105" customFormat="1"/>
-    <row r="106" customFormat="1"/>
     <row r="107" spans="1:12">
       <c r="A107">
         <v>20020011</v>
@@ -12122,8 +12157,6 @@
     <row r="127" customFormat="1" spans="12:12">
       <c r="L127" s="2"/>
     </row>
-    <row r="128" customFormat="1"/>
-    <row r="129" customFormat="1"/>
     <row r="130" spans="1:12">
       <c r="A130">
         <f>A107+1</f>
@@ -12414,8 +12447,6 @@
     <row r="155" spans="1:12">
       <c r="L155" s="2"/>
     </row>
-    <row r="156" customFormat="1"/>
-    <row r="157" customFormat="1"/>
     <row r="158" spans="1:12">
       <c r="A158">
         <f>A130+1</f>
@@ -12706,8 +12737,6 @@
     <row r="183" customFormat="1" spans="1:12">
       <c r="L183" s="2"/>
     </row>
-    <row r="184" customFormat="1"/>
-    <row r="185" customFormat="1"/>
     <row r="186" spans="1:12">
       <c r="A186">
         <f>A158+1</f>
@@ -12998,8 +13027,6 @@
     <row r="211" customFormat="1" spans="1:12">
       <c r="L211" s="2"/>
     </row>
-    <row r="212" customFormat="1"/>
-    <row r="213" customFormat="1"/>
     <row r="214" spans="1:12">
       <c r="A214">
         <f>A186+1</f>
